--- a/data/web/archive/2026-09-05/firis_report.xlsx
+++ b/data/web/archive/2026-09-05/firis_report.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>63.59</v>
+        <v>65.95</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>37.07</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="10">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>40.6</v>
+        <v>40.59</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>28.09</v>
+        <v>30.07</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>56.67</v>
+        <v>56.46</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>24441</v>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>42.82</v>
+        <v>40.8</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>28.5</v>
+        <v>27.05</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>57.03</v>
+        <v>55.04</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>5703</v>
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>26.03</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.43</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>42.89</v>
+        <v>41.93</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>751</v>
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>41.99</v>
+        <v>43.21</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>33.83</v>
+        <v>35.15</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>55.83</v>
+        <v>56.46</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>10563</v>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>38.91</v>
+        <v>36.91</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>33</v>
+        <v>31.01</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>48.25</v>
+        <v>45.76</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1663</v>
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>47.48</v>
+        <v>47.78</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>38.66</v>
+        <v>39.21</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>58.29</v>
+        <v>59.2</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>2137</v>
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>35.93</v>
+        <v>36.32</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1.01</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>53.95</v>
+        <v>54.68</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>1950</v>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>34.52</v>
+        <v>32.72</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>28.08</v>
+        <v>26.42</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>47.26</v>
+        <v>44.43</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>187</v>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>33.93</v>
+        <v>31.17</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>26.4</v>
+        <v>25.61</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>45.42</v>
+        <v>41.3</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>1059</v>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>39.36</v>
+        <v>39.89</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>28.45</v>
+        <v>27.59</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>54.72</v>
+        <v>56.21</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>3976</v>
@@ -1038,13 +1038,13 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44.33</v>
+        <v>42.82</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>33.64</v>
+        <v>32.55</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>59.89</v>
+        <v>58.25</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>5465</v>
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>42.12</v>
+        <v>42.26</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>29.55</v>
+        <v>28.49</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>59.39</v>
+        <v>60.92</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>6849</v>
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>24.14</v>
+        <v>24.44</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>1.06</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>35.74</v>
+        <v>35.71</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>79</v>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>27.87</v>
+        <v>29.38</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0.45</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>46.59</v>
+        <v>49.18</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>932</v>
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>41.68</v>
+        <v>40.76</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>29.62</v>
+        <v>31.15</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>56.66</v>
+        <v>55.92</v>
       </c>
       <c r="G16" s="1" t="n">
         <v>4808</v>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>26.19</v>
+        <v>27.09</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>1.32</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>47.13</v>
+        <v>48.7</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>4944</v>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>34.19</v>
+        <v>33.13</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>0.65</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>52</v>
+        <v>48.85</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>5180</v>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>34.33</v>
+        <v>32.33</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>0.59</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>49.26</v>
+        <v>46.73</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>3925</v>
@@ -1294,13 +1294,13 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45.28</v>
+        <v>43.55</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>35.68</v>
+        <v>33.16</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>55.68</v>
+        <v>55.25</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>657</v>
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>42.14</v>
+        <v>42.24</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>30.97</v>
+        <v>30.92</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>56.66</v>
+        <v>57.16</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>6257</v>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>17.8</v>
+        <v>16.46</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>3.47</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>39.2</v>
+        <v>33.81</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>70</v>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>39.49</v>
+        <v>38.69</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>30.88</v>
+        <v>28.6</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>52.35</v>
+        <v>51.57</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>2293</v>
@@ -1490,13 +1490,13 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>41.52</v>
+        <v>40.47</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>33.08</v>
+        <v>30.6</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>57.1</v>
+        <v>58.75</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>4823</v>
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>23.63</v>
+        <v>23.9</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>0.55</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44.68</v>
+        <v>44.61</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>868</v>
@@ -1554,20 +1554,20 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>39.44</v>
+        <v>40.57</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>32.8</v>
+        <v>34.08</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>50.25</v>
+        <v>51.53</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>466</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1586,13 +1586,13 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>25.73</v>
+        <v>24.17</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>50.74</v>
+        <v>46.19</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>2048</v>
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>31.92</v>
+        <v>30.22</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>6.54</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>39.35</v>
+        <v>37.7</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>173</v>
@@ -1650,20 +1650,20 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>38.55</v>
+        <v>41.35</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>29.39</v>
+        <v>31.75</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>55.73</v>
+        <v>60.92</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>7042</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>21.63</v>
+        <v>21.3</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>42.89</v>
+        <v>41.93</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>66</v>
@@ -1714,20 +1714,20 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>39.59</v>
+        <v>41.06</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>30.19</v>
+        <v>30.15</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>53.27</v>
+        <v>58.02</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>6931</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>زیاد</t>
         </is>
       </c>
     </row>
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>42.3</v>
+        <v>41.13</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>31.22</v>
+        <v>31.5</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>56.08</v>
+        <v>55.01</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>5654</v>
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>36.38</v>
+        <v>36.28</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>3.99</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>54.38</v>
+        <v>52.74</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>16529</v>
@@ -1810,13 +1810,13 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>34.87</v>
+        <v>35.26</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>4.03</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>51.46</v>
+        <v>50.55</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>5265</v>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>41.15</v>
+        <v>41.34</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>32.43</v>
+        <v>32.6</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>54.17</v>
+        <v>55.09</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>2311</v>
@@ -1874,13 +1874,13 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>42.8</v>
+        <v>42.09</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>34.55</v>
+        <v>33.67</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>55.97</v>
+        <v>55.32</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>1185</v>
@@ -1954,7 +1954,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>39049</v>
+        <v>39048</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>4.32</v>
@@ -1973,10 +1973,10 @@
         <v>40</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>531588</v>
+        <v>526146</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>58.76</v>
+        <v>58.15</v>
       </c>
     </row>
     <row r="4">
@@ -1992,10 +1992,10 @@
         <v>60</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>334088</v>
+        <v>339325</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>36.93</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="5">
@@ -2011,10 +2011,10 @@
         <v>80</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>28</v>
+        <v>234</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="6">
